--- a/deliverables/05_manuscript/onki_short_report_table1_characteristics.xlsx
+++ b/deliverables/05_manuscript/onki_short_report_table1_characteristics.xlsx
@@ -9,7 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Table 1'!$3:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Table 1'!$A$1:$C$35</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +31,24 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -37,7 +58,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -51,22 +72,71 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+    </border>
+    <border/>
+    <border>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -432,25 +502,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Table 1. Characteristics of respondents (n=147)</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Characteristic</t>
@@ -461,541 +530,452 @@
           <t>Category</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>n (%)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>18-49 years</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>32 (21.8)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="8" t="inlineStr"/>
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>50-59 years</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>25 (17.0)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="8" t="inlineStr"/>
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>60-69 years</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>61 (41.5)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="8" t="inlineStr"/>
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>≥70 years</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>29 (19.7)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Housing type</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Detached house</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>132 (89.8)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Housing type</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="8" t="inlineStr"/>
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Apartment/condominium</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>15 (10.2)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Building age</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>&lt;30 years</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>62 (42.2)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Building age</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="8" t="inlineStr"/>
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>≥30 years</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>77 (52.4)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Building age</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="8" t="inlineStr"/>
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>8 (5.4)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Tenure</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Owner-occupied</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>130 (88.4)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Tenure</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="8" t="inlineStr"/>
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Rented</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>16 (10.9)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Tenure</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="8" t="inlineStr"/>
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>1 (0.7)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Winter bathing frequency</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>94 (63.9)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Winter bathing frequency</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="8" t="inlineStr"/>
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>4-6 times/week</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>36 (24.5)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Winter bathing frequency</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="8" t="inlineStr"/>
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>1-3 times/week</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>10 (6.8)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Winter bathing frequency</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="8" t="inlineStr"/>
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>1-3 times/month</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>2 (1.4)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Winter bathing frequency</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="8" t="inlineStr"/>
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>Almost never</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>5 (3.4)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Bathroom window</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Double window/double glazing</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>111 (75.5)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Bathroom window</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="8" t="inlineStr"/>
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Single glazing</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>26 (17.7)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Bathroom window</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="8" t="inlineStr"/>
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>No window</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>7 (4.8)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Bathroom window</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="8" t="inlineStr"/>
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Unknown/missing</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>3 (2.0)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Bathroom heater-dryer</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Installed and used</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>35 (23.8)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Bathroom heater-dryer</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="8" t="inlineStr"/>
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Installed but not used</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>13 (8.8)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Bathroom heater-dryer</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="8" t="inlineStr"/>
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Not installed</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>99 (67.3)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Central heating</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Used 24 hours</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>16 (10.9)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Central heating</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="8" t="inlineStr"/>
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Used for limited hours</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>12 (8.2)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Central heating</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="8" t="inlineStr"/>
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Not used</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>112 (76.2)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Central heating</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="8" t="inlineStr"/>
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>7 (4.8)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Perceived coldness</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Bathroom score 5-7</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>66 (44.9)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Perceived coldness</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="11" t="inlineStr"/>
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Dressing-room score 5-7</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>77 (52.4)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="n"/>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Values are n (%). Percentages use all 147 respondents as the denominator. Coldness scores range from 1 (very warm) to 7 (very cold); scores 5-7 indicate perceived coldness.</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/deliverables/05_manuscript/onki_short_report_table1_characteristics.xlsx
+++ b/deliverables/05_manuscript/onki_short_report_table1_characteristics.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Table 1'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Table 1'!$A$1:$C$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Table 1'!$A$1:$C$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -87,6 +87,9 @@
     </border>
     <border/>
     <border>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
       <bottom style="medium">
         <color rgb="00000000"/>
       </bottom>
@@ -127,7 +130,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -504,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -515,7 +518,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Table 1. Characteristics of respondents (n=147)</t>
+          <t>Table 1. Characteristics and heating equipment use in the main analysis sample (n=147)</t>
         </is>
       </c>
     </row>
@@ -841,7 +844,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Installed and used</t>
+          <t>Installed and used for heating</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -854,7 +857,7 @@
       <c r="A26" s="8" t="inlineStr"/>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Installed but not used</t>
+          <t>Installed but not used for heating</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -889,7 +892,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>16 (10.9)</t>
+          <t>16 (11.4)</t>
         </is>
       </c>
     </row>
@@ -902,7 +905,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>12 (8.2)</t>
+          <t>12 (8.6)</t>
         </is>
       </c>
     </row>
@@ -915,7 +918,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>112 (76.2)</t>
+          <t>112 (80.0)</t>
         </is>
       </c>
     </row>
@@ -928,51 +931,137 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>7 (4.8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="38" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Perceived coldness</t>
+          <t>Other equipment used to heat the dressing room or bathroom</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Bathroom score 5-7</t>
+          <t>Stove</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
+          <t>63 (42.9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="8" t="inlineStr"/>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Air conditioner</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>15 (10.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="8" t="inlineStr"/>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Floor heating other than central heating</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>2 (1.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="8" t="inlineStr"/>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>4 (2.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="8" t="inlineStr"/>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>61 (41.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="8" t="inlineStr"/>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>8 (5.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Perceived bathroom coldness</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Score 5-7</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
           <t>66 (44.9)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="11" t="inlineStr"/>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>Dressing-room score 5-7</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="inlineStr">
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>Perceived dressing-room coldness</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>Score 5-7</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>77 (52.4)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>Values are n (%). Percentages use all 147 respondents as the denominator. Coldness scores range from 1 (very warm) to 7 (very cold); scores 5-7 indicate perceived coldness.</t>
+    <row r="41" ht="82" customHeight="1">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>Values are n (%). Percentages for central heating use were calculated among 140 respondents with non-missing data; 7 respondents with missing data are shown separately. Percentages for all other characteristics use all 147 respondents as the denominator. Other equipment used to heat the dressing room or bathroom, excluding the bathroom heater-dryer and central heating, was a multiple-response item; therefore, percentages do not sum to 100%, and missing responses are shown separately. Coldness scores range from 1 (very warm) to 7 (very cold); only the score 5-7 group is shown for each coldness item.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A35:C35"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A41:C41"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/deliverables/05_manuscript/onki_short_report_table1_characteristics.xlsx
+++ b/deliverables/05_manuscript/onki_short_report_table1_characteristics.xlsx
@@ -518,7 +518,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Table 1. Characteristics and heating equipment use in the main analysis sample (n=147)</t>
+          <t>Table 1. Characteristics and heating equipment use in the analysis samples</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>16 (11.4)</t>
+          <t>16 (11.0)</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>12 (8.6)</t>
+          <t>12 (8.3)</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>112 (80.0)</t>
+          <t>117 (80.7)</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
     <row r="41" ht="82" customHeight="1">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Values are n (%). Percentages for central heating use were calculated among 140 respondents with non-missing data; 7 respondents with missing data are shown separately. Percentages for all other characteristics use all 147 respondents as the denominator. Other equipment used to heat the dressing room or bathroom, excluding the bathroom heater-dryer and central heating, was a multiple-response item; therefore, percentages do not sum to 100%, and missing responses are shown separately. Coldness scores range from 1 (very warm) to 7 (very cold); only the score 5-7 group is shown for each coldness item.</t>
+          <t>Values are n (%). Percentages for central heating use were calculated among 145 respondents with non-missing data; 9 of 154 returned questionnaires had missing data and are shown separately. Percentages for all other characteristics use all 147 respondents in the primary analysis as the denominator. Other equipment used to heat the dressing room or bathroom, excluding the bathroom heater-dryer and central heating, was a multiple-response item; therefore, percentages do not sum to 100%, and missing responses are shown separately. Coldness scores range from 1 (very warm) to 7 (very cold); only the score 5-7 group is shown for each coldness item.</t>
         </is>
       </c>
     </row>

--- a/deliverables/05_manuscript/onki_short_report_table1_characteristics.xlsx
+++ b/deliverables/05_manuscript/onki_short_report_table1_characteristics.xlsx
@@ -839,7 +839,7 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Bathroom heater-dryer</t>
+          <t>Bathroom heating dryer</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1054,7 +1054,7 @@
     <row r="41" ht="82" customHeight="1">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Values are n (%). Percentages for central heating use were calculated among 145 respondents with non-missing data; 9 of 154 returned questionnaires had missing data and are shown separately. Percentages for all other characteristics use all 147 respondents in the primary analysis as the denominator. Other equipment used to heat the dressing room or bathroom, excluding the bathroom heater-dryer and central heating, was a multiple-response item; therefore, percentages do not sum to 100%, and missing responses are shown separately. Coldness scores range from 1 (very warm) to 7 (very cold); only the score 5-7 group is shown for each coldness item.</t>
+          <t>Values are n (%). Percentages for central heating use were calculated among 145 respondents with non-missing data; 9 of 154 returned questionnaires had missing data and are shown separately. Percentages for all other characteristics use all 147 respondents in the primary analysis as the denominator. Other equipment used to heat the dressing room or bathroom, excluding the bathroom heating dryer and central heating, was a multiple-response item; therefore, percentages do not sum to 100%, and missing responses are shown separately. Coldness scores range from 1 (very warm) to 7 (very cold); only the score 5-7 group is shown for each coldness item.</t>
         </is>
       </c>
     </row>

--- a/deliverables/05_manuscript/onki_short_report_table1_characteristics.xlsx
+++ b/deliverables/05_manuscript/onki_short_report_table1_characteristics.xlsx
@@ -518,7 +518,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Table 1. Characteristics and heating equipment use in the analysis samples</t>
+          <t>Table 1. Characteristics and use of heating equipment in the primary analysis sample (n = 147)</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Tenure</t>
+          <t>Housing tenure</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -711,10 +711,10 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
+    <row r="16" ht="42" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Winter bathing frequency</t>
+          <t>Frequency of bathing at home in winter</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Used 24 hours</t>
+          <t>Used 24 h/day (continuous)</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Stove</t>
+          <t>Space heater (stove)</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -969,7 +969,7 @@
       <c r="A34" s="8" t="inlineStr"/>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Floor heating other than central heating</t>
+          <t>Floor heating not part of the central heating system</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Score 5-7</t>
+          <t>Coldness score 5-7</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Score 5-7</t>
+          <t>Coldness score 5-7</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
@@ -1054,7 +1054,7 @@
     <row r="41" ht="82" customHeight="1">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Values are n (%). Percentages for central heating use were calculated among 145 respondents with non-missing data; 9 of 154 returned questionnaires had missing data and are shown separately. Percentages for all other characteristics use all 147 respondents in the primary analysis as the denominator. Other equipment used to heat the dressing room or bathroom, excluding the bathroom heating dryer and central heating, was a multiple-response item; therefore, percentages do not sum to 100%, and missing responses are shown separately. Coldness scores range from 1 (very warm) to 7 (very cold); only the score 5-7 group is shown for each coldness item.</t>
+          <t>Values are n (%). For central heating use, 145 of the 154 returned questionnaires had non-missing data; the nine missing responses are shown separately. Percentages for all other characteristics were calculated with all 147 respondents in the primary analysis as the denominator. Use of other equipment to heat the dressing room or bathroom, excluding the bathroom heating dryer and central heating, was assessed with a multiple-response item; therefore, percentages do not sum to 100%, and missing responses are shown separately. Perceived thermal sensation in the bathroom and dressing room was rated on a 7-point scale from 1 (very warm) to 7 (very cold); for each room, only the derived coldness score 5-7 group is shown.</t>
         </is>
       </c>
     </row>

--- a/deliverables/05_manuscript/onki_short_report_table1_characteristics.xlsx
+++ b/deliverables/05_manuscript/onki_short_report_table1_characteristics.xlsx
@@ -1054,7 +1054,7 @@
     <row r="41" ht="82" customHeight="1">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Values are n (%). For central heating use, 145 of the 154 returned questionnaires had non-missing data; the nine missing responses are shown separately. Percentages for all other characteristics were calculated with all 147 respondents in the primary analysis as the denominator. Use of other equipment to heat the dressing room or bathroom, excluding the bathroom heating dryer and central heating, was assessed with a multiple-response item; therefore, percentages do not sum to 100%, and missing responses are shown separately. Perceived thermal sensation in the bathroom and dressing room was rated on a 7-point scale from 1 (very warm) to 7 (very cold); for each room, only the derived coldness score 5-7 group is shown.</t>
+          <t>Values are n (%). For central heating use, 145 of the 154 returned questionnaires had non-missing data; the nine missing responses are shown in a separate row without a percentage. Percentages for all other characteristics were calculated with all 147 respondents in the primary analysis as the denominator. Use of other equipment to heat the dressing room or bathroom, excluding the bathroom heating dryer and central heating, was assessed with a multiple-response item; therefore, percentages do not sum to 100%. The eight missing responses to this item are shown in a separate row, with the percentage calculated using the 147 respondents as the denominator. For the bathroom and dressing room, perceived thermal sensation was rated on a 7-point scale from 1 (very warm) to 7 (very cold), and the ratings were treated as the respective coldness scores; only the coldness score 5-7 group is shown for each room.</t>
         </is>
       </c>
     </row>

--- a/deliverables/05_manuscript/onki_short_report_table1_characteristics.xlsx
+++ b/deliverables/05_manuscript/onki_short_report_table1_characteristics.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>18-49 years</t>
+          <t>18–49 years</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -560,7 +560,7 @@
       <c r="A5" s="8" t="inlineStr"/>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>50-59 years</t>
+          <t>50–59 years</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -573,7 +573,7 @@
       <c r="A6" s="8" t="inlineStr"/>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>60-69 years</t>
+          <t>60–69 years</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -732,7 +732,7 @@
       <c r="A17" s="8" t="inlineStr"/>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>4-6 times/week</t>
+          <t>4–6 times/week</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -745,7 +745,7 @@
       <c r="A18" s="8" t="inlineStr"/>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>1-3 times/week</t>
+          <t>1–3 times/week</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -758,7 +758,7 @@
       <c r="A19" s="8" t="inlineStr"/>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>1-3 times/month</t>
+          <t>1–3 times/month</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Coldness score 5-7</t>
+          <t>Coldness score 5–7</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Coldness score 5-7</t>
+          <t>Coldness score 5–7</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
@@ -1054,7 +1054,7 @@
     <row r="41" ht="82" customHeight="1">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Values are n (%). For central heating use, 145 of the 154 returned questionnaires had non-missing data; the nine missing responses are shown in a separate row without a percentage. Percentages for all other characteristics were calculated with all 147 respondents in the primary analysis as the denominator. Use of other equipment to heat the dressing room or bathroom, excluding the bathroom heating dryer and central heating, was assessed with a multiple-response item; therefore, percentages do not sum to 100%. The eight missing responses to this item are shown in a separate row, with the percentage calculated using the 147 respondents as the denominator. For the bathroom and dressing room, perceived thermal sensation was rated on a 7-point scale from 1 (very warm) to 7 (very cold), and the ratings were treated as the respective coldness scores; only the coldness score 5-7 group is shown for each room.</t>
+          <t>Values are presented as n (%). For central-heating use, 145 of the 154 returned questionnaires had no missing data; the 9 missing responses are shown in a separate row without a percentage. Percentages for all other characteristics were calculated using the 147 respondents in the primary analysis as the denominator. The use of other equipment to heat the dressing room or bathroom, excluding the bathroom heating dryer and central heating, was assessed using a multiple-response item; therefore, the percentages do not sum to 100%. The 8 missing responses for this item are shown in a separate row, with the percentage calculated using the 147 respondents as the denominator. For the bathroom and dressing room, perceived thermal sensation was rated on a 7-point scale, from 1 (very warm) to 7 (very cold): the ratings were treated as the respective coldness scores; only the coldness score 5–7 group is shown for each room.</t>
         </is>
       </c>
     </row>
